--- a/tour-finance/output/raw_extract.xlsx
+++ b/tour-finance/output/raw_extract.xlsx
@@ -592,6 +592,9 @@
       <c r="I2" t="n">
         <v>-48.5</v>
       </c>
+      <c r="J2" t="n">
+        <v>-48.53</v>
+      </c>
       <c r="K2" t="n">
         <v>136.25</v>
       </c>
@@ -808,6 +811,9 @@
       <c r="I5" t="n">
         <v>-210.62</v>
       </c>
+      <c r="J5" t="n">
+        <v>-209.09</v>
+      </c>
       <c r="K5" t="n">
         <v>136.25</v>
       </c>
@@ -878,6 +884,9 @@
       <c r="I6" t="n">
         <v>-49.98</v>
       </c>
+      <c r="J6" t="n">
+        <v>-49.92</v>
+      </c>
       <c r="K6" t="n">
         <v>134.45</v>
       </c>
@@ -1094,6 +1103,9 @@
       <c r="I9" t="n">
         <v>-112.27</v>
       </c>
+      <c r="J9" t="n">
+        <v>-111.45</v>
+      </c>
       <c r="K9" t="n">
         <v>134.45</v>
       </c>
@@ -1164,6 +1176,9 @@
       <c r="I10" t="n">
         <v>-13.24</v>
       </c>
+      <c r="J10" t="n">
+        <v>-11.58</v>
+      </c>
       <c r="K10" t="n">
         <v>137.68</v>
       </c>
@@ -1380,6 +1395,9 @@
       <c r="I13" t="n">
         <v>-60.57</v>
       </c>
+      <c r="J13" t="n">
+        <v>-54.26</v>
+      </c>
       <c r="K13" t="n">
         <v>137.68</v>
       </c>
@@ -1450,6 +1468,9 @@
       <c r="I14" t="n">
         <v>0.72</v>
       </c>
+      <c r="J14" t="n">
+        <v>1.64</v>
+      </c>
       <c r="K14" t="n">
         <v>122.04</v>
       </c>
@@ -1666,6 +1687,9 @@
       <c r="I17" t="n">
         <v>-5.6</v>
       </c>
+      <c r="J17" t="n">
+        <v>-2.18</v>
+      </c>
       <c r="K17" t="n">
         <v>122.04</v>
       </c>
@@ -1736,6 +1760,9 @@
       <c r="I18" t="n">
         <v>14.42</v>
       </c>
+      <c r="J18" t="n">
+        <v>14.96</v>
+      </c>
       <c r="K18" t="n">
         <v>87.28</v>
       </c>
@@ -1952,6 +1979,9 @@
       <c r="I21" t="n">
         <v>-3.35</v>
       </c>
+      <c r="J21" t="n">
+        <v>-1.13</v>
+      </c>
       <c r="K21" t="n">
         <v>87.28</v>
       </c>
@@ -4934,7 +4964,7 @@
         <v>390.06</v>
       </c>
       <c r="G62" t="n">
-        <v>11.43</v>
+        <v>16.64</v>
       </c>
       <c r="H62" t="n">
         <v>315.03</v>
@@ -4942,6 +4972,9 @@
       <c r="I62" t="n">
         <v>-512.88</v>
       </c>
+      <c r="J62" t="n">
+        <v>-491.94</v>
+      </c>
       <c r="K62" t="n">
         <v>76.59</v>
       </c>
@@ -5158,6 +5191,9 @@
       <c r="I65" t="n">
         <v>-2155.37</v>
       </c>
+      <c r="J65" t="n">
+        <v>-2050.22</v>
+      </c>
       <c r="K65" t="n">
         <v>76.59</v>
       </c>
@@ -5220,7 +5256,7 @@
         <v>646.09</v>
       </c>
       <c r="G66" t="n">
-        <v>7.28</v>
+        <v>12.49</v>
       </c>
       <c r="H66" t="n">
         <v>404.82</v>
@@ -5228,6 +5264,9 @@
       <c r="I66" t="n">
         <v>-324.86</v>
       </c>
+      <c r="J66" t="n">
+        <v>-313.1</v>
+      </c>
       <c r="K66" t="n">
         <v>99.84999999999999</v>
       </c>
@@ -5444,6 +5483,9 @@
       <c r="I69" t="n">
         <v>-213.06</v>
       </c>
+      <c r="J69" t="n">
+        <v>-224.19</v>
+      </c>
       <c r="K69" t="n">
         <v>99.84999999999999</v>
       </c>
@@ -5506,7 +5548,7 @@
         <v>1774.62</v>
       </c>
       <c r="G70" t="n">
-        <v>20.23</v>
+        <v>25.44</v>
       </c>
       <c r="H70" t="n">
         <v>775.23</v>
@@ -5514,6 +5556,9 @@
       <c r="I70" t="n">
         <v>237.39</v>
       </c>
+      <c r="J70" t="n">
+        <v>238.56</v>
+      </c>
       <c r="K70" t="n">
         <v>159.81</v>
       </c>
@@ -5730,6 +5775,9 @@
       <c r="I73" t="n">
         <v>759.88</v>
       </c>
+      <c r="J73" t="n">
+        <v>742.66</v>
+      </c>
       <c r="K73" t="n">
         <v>159.81</v>
       </c>
@@ -5800,6 +5848,9 @@
       <c r="I74" t="n">
         <v>428.4</v>
       </c>
+      <c r="J74" t="n">
+        <v>416.95</v>
+      </c>
       <c r="K74" t="n">
         <v>169.83</v>
       </c>
@@ -6016,6 +6067,9 @@
       <c r="I77" t="n">
         <v>1312.51</v>
       </c>
+      <c r="J77" t="n">
+        <v>1280.74</v>
+      </c>
       <c r="K77" t="n">
         <v>169.83</v>
       </c>
@@ -6086,6 +6140,9 @@
       <c r="I78" t="n">
         <v>362.74</v>
       </c>
+      <c r="J78" t="n">
+        <v>345.38</v>
+      </c>
       <c r="K78" t="n">
         <v>222.44</v>
       </c>
@@ -6156,6 +6213,9 @@
       <c r="I79" t="n">
         <v>69.78</v>
       </c>
+      <c r="J79" t="n">
+        <v>63.01</v>
+      </c>
       <c r="K79" t="n">
         <v>222.44</v>
       </c>
@@ -6299,6 +6359,9 @@
       <c r="I81" t="n">
         <v>904.76</v>
       </c>
+      <c r="J81" t="n">
+        <v>838.09</v>
+      </c>
       <c r="K81" t="n">
         <v>222.44</v>
       </c>
@@ -6369,6 +6432,9 @@
       <c r="I82" t="n">
         <v>-16.49</v>
       </c>
+      <c r="J82" t="n">
+        <v>-16.49</v>
+      </c>
       <c r="K82" t="n">
         <v>3.03</v>
       </c>
@@ -6439,6 +6505,9 @@
       <c r="I83" t="n">
         <v>-39.07</v>
       </c>
+      <c r="J83" t="n">
+        <v>-39.07</v>
+      </c>
       <c r="K83" t="n">
         <v>3.03</v>
       </c>
@@ -6509,6 +6578,9 @@
       <c r="I84" t="n">
         <v>-26.51</v>
       </c>
+      <c r="J84" t="n">
+        <v>-26.51</v>
+      </c>
       <c r="K84" t="n">
         <v>3.03</v>
       </c>
@@ -6579,6 +6651,9 @@
       <c r="I85" t="n">
         <v>-48.84</v>
       </c>
+      <c r="J85" t="n">
+        <v>-48.84</v>
+      </c>
       <c r="K85" t="n">
         <v>3.03</v>
       </c>
@@ -6649,6 +6724,9 @@
       <c r="I86" t="n">
         <v>-30.29</v>
       </c>
+      <c r="J86" t="n">
+        <v>-30.29</v>
+      </c>
       <c r="K86" t="n">
         <v>5.77</v>
       </c>
@@ -6719,6 +6797,9 @@
       <c r="I87" t="n">
         <v>-42.34</v>
       </c>
+      <c r="J87" t="n">
+        <v>-42.34</v>
+      </c>
       <c r="K87" t="n">
         <v>5.77</v>
       </c>
@@ -6789,6 +6870,9 @@
       <c r="I88" t="n">
         <v>-46.85</v>
       </c>
+      <c r="J88" t="n">
+        <v>-46.85</v>
+      </c>
       <c r="K88" t="n">
         <v>5.77</v>
       </c>
@@ -6859,6 +6943,9 @@
       <c r="I89" t="n">
         <v>-39.89</v>
       </c>
+      <c r="J89" t="n">
+        <v>-39.89</v>
+      </c>
       <c r="K89" t="n">
         <v>5.77</v>
       </c>
@@ -6929,6 +7016,9 @@
       <c r="I90" t="n">
         <v>6.84</v>
       </c>
+      <c r="J90" t="n">
+        <v>6.84</v>
+      </c>
       <c r="K90" t="n">
         <v>10.38</v>
       </c>
@@ -6999,6 +7089,9 @@
       <c r="I91" t="n">
         <v>8.039999999999999</v>
       </c>
+      <c r="J91" t="n">
+        <v>8.039999999999999</v>
+      </c>
       <c r="K91" t="n">
         <v>10.38</v>
       </c>
@@ -7069,6 +7162,9 @@
       <c r="I92" t="n">
         <v>23.41</v>
       </c>
+      <c r="J92" t="n">
+        <v>23.41</v>
+      </c>
       <c r="K92" t="n">
         <v>10.38</v>
       </c>
@@ -7139,6 +7235,9 @@
       <c r="I93" t="n">
         <v>34.68</v>
       </c>
+      <c r="J93" t="n">
+        <v>34.68</v>
+      </c>
       <c r="K93" t="n">
         <v>10.38</v>
       </c>
@@ -7209,6 +7308,9 @@
       <c r="I94" t="n">
         <v>13.79</v>
       </c>
+      <c r="J94" t="n">
+        <v>13.79</v>
+      </c>
       <c r="K94" t="n">
         <v>12.26</v>
       </c>
@@ -7279,6 +7381,9 @@
       <c r="I95" t="n">
         <v>6.88</v>
       </c>
+      <c r="J95" t="n">
+        <v>6.88</v>
+      </c>
       <c r="K95" t="n">
         <v>12.24</v>
       </c>
@@ -7349,6 +7454,9 @@
       <c r="I96" t="n">
         <v>18.19</v>
       </c>
+      <c r="J96" t="n">
+        <v>18.19</v>
+      </c>
       <c r="K96" t="n">
         <v>12.24</v>
       </c>
@@ -7419,6 +7527,9 @@
       <c r="I97" t="n">
         <v>50.82</v>
       </c>
+      <c r="J97" t="n">
+        <v>50.82</v>
+      </c>
       <c r="K97" t="n">
         <v>12.24</v>
       </c>
@@ -7489,6 +7600,9 @@
       <c r="I98" t="n">
         <v>14.11</v>
       </c>
+      <c r="J98" t="n">
+        <v>14.11</v>
+      </c>
       <c r="K98" t="n">
         <v>13.22</v>
       </c>
@@ -7559,6 +7673,9 @@
       <c r="I99" t="n">
         <v>3.67</v>
       </c>
+      <c r="J99" t="n">
+        <v>3.67</v>
+      </c>
       <c r="K99" t="n">
         <v>13.22</v>
       </c>
@@ -7629,6 +7746,9 @@
       <c r="I100" t="n">
         <v>11.84</v>
       </c>
+      <c r="J100" t="n">
+        <v>11.84</v>
+      </c>
       <c r="K100" t="n">
         <v>13.22</v>
       </c>
@@ -7699,6 +7819,9 @@
       <c r="I101" t="n">
         <v>39.82</v>
       </c>
+      <c r="J101" t="n">
+        <v>39.82</v>
+      </c>
       <c r="K101" t="n">
         <v>13.22</v>
       </c>
@@ -12149,6 +12272,9 @@
       <c r="I162" t="n">
         <v>-310.9</v>
       </c>
+      <c r="J162" t="n">
+        <v>-310.9</v>
+      </c>
       <c r="K162" t="n">
         <v>52.3</v>
       </c>
@@ -12219,6 +12345,9 @@
       <c r="I163" t="n">
         <v>-571.4299999999999</v>
       </c>
+      <c r="J163" t="n">
+        <v>-571.4299999999999</v>
+      </c>
       <c r="K163" t="n">
         <v>52.3</v>
       </c>
@@ -12289,6 +12418,9 @@
       <c r="I164" t="n">
         <v>-281.86</v>
       </c>
+      <c r="J164" t="n">
+        <v>-281.86</v>
+      </c>
       <c r="K164" t="n">
         <v>52.3</v>
       </c>
@@ -12359,6 +12491,9 @@
       <c r="I165" t="n">
         <v>-1234.22</v>
       </c>
+      <c r="J165" t="n">
+        <v>-1234.22</v>
+      </c>
       <c r="K165" t="n">
         <v>52.3</v>
       </c>
@@ -12429,6 +12564,9 @@
       <c r="I166" t="n">
         <v>-204.09</v>
       </c>
+      <c r="J166" t="n">
+        <v>-204.09</v>
+      </c>
       <c r="K166" t="n">
         <v>387.23</v>
       </c>
@@ -12499,6 +12637,9 @@
       <c r="I167" t="n">
         <v>-96.88</v>
       </c>
+      <c r="J167" t="n">
+        <v>-96.88</v>
+      </c>
       <c r="K167" t="n">
         <v>387.23</v>
       </c>
@@ -12569,6 +12710,9 @@
       <c r="I168" t="n">
         <v>207.48</v>
       </c>
+      <c r="J168" t="n">
+        <v>207.48</v>
+      </c>
       <c r="K168" t="n">
         <v>387.23</v>
       </c>
@@ -12639,6 +12783,9 @@
       <c r="I169" t="n">
         <v>14.38</v>
       </c>
+      <c r="J169" t="n">
+        <v>14.38</v>
+      </c>
       <c r="K169" t="n">
         <v>387.23</v>
       </c>
@@ -12709,6 +12856,9 @@
       <c r="I170" t="n">
         <v>124.88</v>
       </c>
+      <c r="J170" t="n">
+        <v>124.88</v>
+      </c>
       <c r="K170" t="n">
         <v>501.36</v>
       </c>
@@ -12779,6 +12929,9 @@
       <c r="I171" t="n">
         <v>3</v>
       </c>
+      <c r="J171" t="n">
+        <v>-117.22</v>
+      </c>
       <c r="K171" t="n">
         <v>501.36</v>
       </c>
@@ -12849,6 +13002,9 @@
       <c r="I172" t="n">
         <v>15.01</v>
       </c>
+      <c r="J172" t="n">
+        <v>15.01</v>
+      </c>
       <c r="K172" t="n">
         <v>501.36</v>
       </c>
@@ -12919,6 +13075,9 @@
       <c r="I173" t="n">
         <v>86.41</v>
       </c>
+      <c r="J173" t="n">
+        <v>86.41</v>
+      </c>
       <c r="K173" t="n">
         <v>501.36</v>
       </c>
@@ -12989,6 +13148,9 @@
       <c r="I174" t="n">
         <v>111.62</v>
       </c>
+      <c r="J174" t="n">
+        <v>111.62</v>
+      </c>
       <c r="K174" t="n">
         <v>534.5599999999999</v>
       </c>
@@ -13059,6 +13221,9 @@
       <c r="I175" t="n">
         <v>-71.59</v>
       </c>
+      <c r="J175" t="n">
+        <v>-71.59</v>
+      </c>
       <c r="K175" t="n">
         <v>534.5599999999999</v>
       </c>
@@ -13129,6 +13294,9 @@
       <c r="I176" t="n">
         <v>-53.4</v>
       </c>
+      <c r="J176" t="n">
+        <v>-53.4</v>
+      </c>
       <c r="K176" t="n">
         <v>534.5599999999999</v>
       </c>
@@ -13199,6 +13367,9 @@
       <c r="I177" t="n">
         <v>133.93</v>
       </c>
+      <c r="J177" t="n">
+        <v>133.93</v>
+      </c>
       <c r="K177" t="n">
         <v>534.5599999999999</v>
       </c>
@@ -13269,6 +13440,9 @@
       <c r="I178" t="n">
         <v>175.54</v>
       </c>
+      <c r="J178" t="n">
+        <v>175.54</v>
+      </c>
       <c r="K178" t="n">
         <v>475.75</v>
       </c>
@@ -13339,6 +13513,9 @@
       <c r="I179" t="n">
         <v>24.22</v>
       </c>
+      <c r="J179" t="n">
+        <v>24.22</v>
+      </c>
       <c r="K179" t="n">
         <v>475.75</v>
       </c>
@@ -13409,6 +13586,9 @@
       <c r="I180" t="n">
         <v>128.59</v>
       </c>
+      <c r="J180" t="n">
+        <v>128.59</v>
+      </c>
       <c r="K180" t="n">
         <v>475.75</v>
       </c>
@@ -13479,6 +13659,9 @@
       <c r="I181" t="n">
         <v>-1586.05</v>
       </c>
+      <c r="J181" t="n">
+        <v>-1586.05</v>
+      </c>
       <c r="K181" t="n">
         <v>475.75</v>
       </c>
@@ -13766,6 +13949,9 @@
         <v>433.73</v>
       </c>
       <c r="I185" t="n">
+        <v>-107.25</v>
+      </c>
+      <c r="J185" t="n">
         <v>-107.25</v>
       </c>
       <c r="K185" t="n">
